--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T18:38:38+00:00</t>
+    <t>2026-09-03T18:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-dosage-standard-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T18:40:45+00:00</t>
+    <t>2026-09-10T13:22:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
